--- a/Data/Velavan Material Expense.xlsx
+++ b/Data/Velavan Material Expense.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/Vellavan Site Saravanampatty/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{C19A66FE-B7FE-414A-9AFE-7C8069596151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8EC244A-221E-41B3-93AD-7F60B6B9F6D9}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{A5FE4F82-6AAE-4F54-BB88-799A0B08B3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B42873B9-33F0-4DF6-AC19-17EAED2A9923}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="75">
   <si>
     <t>DATE</t>
   </si>
@@ -277,6 +277,18 @@
   </si>
   <si>
     <t>Balance amt closing</t>
+  </si>
+  <si>
+    <t>5000 nos</t>
+  </si>
+  <si>
+    <t>Full Amt TATA</t>
+  </si>
+  <si>
+    <t>MALAR TRADERS</t>
+  </si>
+  <si>
+    <t>Full Amt</t>
   </si>
 </sst>
 </file>
@@ -314,7 +326,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -433,6 +445,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -473,7 +496,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultColWidth="25.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="20" bestFit="1" customWidth="1"/>
@@ -2036,7 +2059,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="13">
+      <c r="A42" s="11">
         <v>46092</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -2057,111 +2080,111 @@
       <c r="G42" s="7">
         <v>2000</v>
       </c>
-      <c r="H42" s="14">
+      <c r="H42" s="9">
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
         <v>24000</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="21">
+      <c r="A43" s="11">
         <v>46093</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22" t="s">
+      <c r="C43" s="6"/>
+      <c r="D43" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="6">
         <v>4</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="7">
         <v>5250</v>
       </c>
-      <c r="H43" s="24">
+      <c r="H43" s="9">
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
         <v>21000</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="21">
+      <c r="A44" s="11">
         <v>46094</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="D44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="6">
         <v>10000</v>
       </c>
-      <c r="F44" s="22" t="s">
+      <c r="F44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="7">
         <v>12</v>
       </c>
-      <c r="H44" s="24">
+      <c r="H44" s="9">
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
         <v>120000</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="21">
+      <c r="A45" s="11">
         <v>46101</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22" t="s">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="6">
         <v>4</v>
       </c>
-      <c r="F45" s="22" t="s">
+      <c r="F45" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="7">
         <v>5250</v>
       </c>
-      <c r="H45" s="24">
+      <c r="H45" s="9">
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
         <v>21000</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="21">
+      <c r="A46" s="11">
         <v>46101</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="6">
         <v>50</v>
       </c>
-      <c r="F46" s="22" t="s">
+      <c r="F46" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="7">
         <v>300</v>
       </c>
-      <c r="H46" s="24">
+      <c r="H46" s="9">
         <f>Table1[[#This Row],[QTY]]*Table1[[#This Row],[RATE]]</f>
         <v>15000</v>
       </c>
@@ -2434,6 +2457,230 @@
       <c r="H57" s="9">
         <f>E57*G57</f>
         <v>21000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="11">
+        <v>46152</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" s="7"/>
+      <c r="H58" s="9">
+        <v>106210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="11">
+        <v>46155</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="6">
+        <v>5000</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="7">
+        <v>12</v>
+      </c>
+      <c r="H59" s="9">
+        <f>E59*G59</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="11">
+        <v>46158</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="6">
+        <v>4</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="7">
+        <v>5250</v>
+      </c>
+      <c r="H60" s="9">
+        <f>G60*E60</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="11">
+        <v>46164</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="6">
+        <v>3503</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="7"/>
+      <c r="H61" s="9">
+        <v>306000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="11">
+        <v>46165</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" s="6">
+        <v>50</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="7">
+        <v>325</v>
+      </c>
+      <c r="H62" s="9">
+        <f>E62*G62</f>
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="11">
+        <v>46176</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="6">
+        <v>4</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="7">
+        <v>5250</v>
+      </c>
+      <c r="H63" s="9">
+        <f>E63*G63</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="11">
+        <v>46177</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="6">
+        <v>150</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="7">
+        <v>313</v>
+      </c>
+      <c r="H64" s="9">
+        <f>E64*G64</f>
+        <v>46950</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="11">
+        <v>46177</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="6">
+        <v>8</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="7">
+        <v>4625</v>
+      </c>
+      <c r="H65" s="9">
+        <f>E65*G65</f>
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="11">
+        <v>46177</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="9">
+        <v>12792</v>
       </c>
     </row>
   </sheetData>
@@ -2619,14 +2866,14 @@
       </c>
       <c r="B2" s="6">
         <f>SUMIF('Material Details'!B2:B1009,A2,'Material Details'!E2:E1009)</f>
-        <v>8541.4</v>
+        <v>13244.4</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="7">
         <f>SUMIF('Material Details'!B2:B1009,A2,'Material Details'!H2:H1009)</f>
-        <v>1051615.83</v>
+        <v>1463825.83</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -2635,14 +2882,14 @@
       </c>
       <c r="B3" s="6">
         <f>SUMIF('Material Details'!B3:B1010,A3,'Material Details'!E3:E1010)</f>
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="7">
         <f>SUMIF('Material Details'!B3:B1010,A3,'Material Details'!H3:H1010)</f>
-        <v>284000</v>
+        <v>326000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2667,14 +2914,14 @@
       </c>
       <c r="B5" s="6">
         <f>SUMIF('Material Details'!B5:B1012,A5,'Material Details'!E5:E1012)</f>
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="7">
         <f>SUMIF('Material Details'!B5:B1012,A5,'Material Details'!H5:H1012)</f>
-        <v>350800</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -2683,14 +2930,14 @@
       </c>
       <c r="B6" s="6">
         <f>SUMIF('Material Details'!B6:B1013,A6,'Material Details'!E6:E1013)</f>
-        <v>44012</v>
+        <v>49012</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="7">
         <f>SUMIF('Material Details'!B6:B1013,A6,'Material Details'!H6:H1013)</f>
-        <v>553200</v>
+        <v>613200</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -2699,14 +2946,14 @@
       </c>
       <c r="B7" s="6">
         <f>SUMIF('Material Details'!B8:B1014,A7,'Material Details'!E8:E1014)</f>
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="7">
         <f>SUMIF('Material Details'!B7:B1014,A7,'Material Details'!H7:H1014)</f>
-        <v>176500</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -2754,7 +3001,7 @@
       </c>
       <c r="D10" s="7">
         <f>SUMIF('Material Details'!B10:B1017,A10,'Material Details'!H10:H1017)</f>
-        <v>12515</v>
+        <v>25307</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -2769,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96697B0-05D6-4BCA-A61B-0D246D1FF2DE}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.54296875" bestFit="1" customWidth="1"/>
@@ -2796,20 +3043,20 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="str" cm="1">
-        <f t="array" ref="A2:A12">_xlfn.UNIQUE('Material Details'!D2:D1009)</f>
+        <f t="array" ref="A2:A13">_xlfn.UNIQUE('Material Details'!D2:D1009)</f>
         <v>AK STEELS</v>
       </c>
       <c r="B2" s="7">
         <f>SUMIF('Material Details'!D2:D1009,A2,'Material Details'!H2:H1009)</f>
-        <v>1051615.83</v>
+        <v>1463825.83</v>
       </c>
       <c r="C2" s="7">
         <f>SUMIF('Payment Details'!B2:B1001,'Vendor Balance Sheet'!A2,'Payment Details'!C2:C1001)</f>
-        <v>957000</v>
+        <v>1463000</v>
       </c>
       <c r="D2" s="7">
         <f>B2-C2</f>
-        <v>94615.830000000075</v>
+        <v>825.83000000007451</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2818,15 +3065,15 @@
       </c>
       <c r="B3" s="7">
         <f>SUMIF('Material Details'!D2:D1009,A3,'Material Details'!H2:H1009)</f>
-        <v>526400</v>
+        <v>605400</v>
       </c>
       <c r="C3" s="7">
         <f>SUMIF('Payment Details'!B3:B1002,'Vendor Balance Sheet'!A3,'Payment Details'!C3:C1002)</f>
-        <v>500000</v>
+        <v>539000</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3-C3</f>
-        <v>26400</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -2852,11 +3099,11 @@
       </c>
       <c r="B5" s="7">
         <f>SUMIF('Material Details'!D4:D1011,A5,'Material Details'!H4:H1011)</f>
-        <v>553200</v>
+        <v>613200</v>
       </c>
       <c r="C5" s="7">
         <f>SUMIF('Payment Details'!B3:B1002,'Vendor Balance Sheet'!A5,'Payment Details'!C3:C1002)</f>
-        <v>553200</v>
+        <v>613200</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
@@ -2890,11 +3137,11 @@
       </c>
       <c r="C7" s="7">
         <f>SUMIF('Payment Details'!B5:B1004,'Vendor Balance Sheet'!A7,'Payment Details'!C5:C1004)</f>
-        <v>145900</v>
+        <v>146200</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -2937,11 +3184,11 @@
       </c>
       <c r="B10" s="7">
         <f>SUMIF('Material Details'!D10:D1016,A10,'Material Details'!H10:H1016)</f>
-        <v>89500</v>
+        <v>105750</v>
       </c>
       <c r="C10" s="7">
         <f>SUMIF('Payment Details'!B8:B1007,'Vendor Balance Sheet'!A10,'Payment Details'!C8:C1007)</f>
-        <v>89500</v>
+        <v>105750</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" ref="D10:D11" si="2">B10-C10</f>
@@ -2954,7 +3201,7 @@
       </c>
       <c r="B11" s="7">
         <f>SUMIF('Material Details'!D11:D1017,A11,'Material Details'!H11:H1017)</f>
-        <v>12515</v>
+        <v>25307</v>
       </c>
       <c r="C11" s="7">
         <f>SUMIF('Payment Details'!B9:B1008,'Vendor Balance Sheet'!A11,'Payment Details'!C9:C1008)</f>
@@ -2962,11 +3209,28 @@
       </c>
       <c r="D11" s="7">
         <f t="shared" si="2"/>
-        <v>2515</v>
+        <v>15307</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="A12" t="str">
+        <v>MALAR TRADERS</v>
+      </c>
+      <c r="B12" s="7">
+        <f>SUMIF('Material Details'!D12:D1018,A12,'Material Details'!H12:H1018)</f>
+        <v>46950</v>
+      </c>
+      <c r="C12" s="7">
+        <f>SUMIF('Payment Details'!B10:B1009,'Vendor Balance Sheet'!A12,'Payment Details'!C10:C1009)</f>
+        <v>46950</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" ref="D12" si="3">B12-C12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>0</v>
       </c>
     </row>
@@ -2977,7 +3241,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B843CC5F-739E-45E9-AC65-8442CF552E38}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="3"/>
@@ -3396,7 +3660,7 @@
         <v>46</v>
       </c>
       <c r="C21" s="7">
-        <v>5900</v>
+        <v>6200</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>28</v>
@@ -3732,7 +3996,7 @@
       <c r="A38" s="5">
         <v>46144</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C38" s="7">
@@ -3744,7 +4008,7 @@
       <c r="E38" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="F38" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3752,7 +4016,7 @@
       <c r="A39" s="5">
         <v>46144</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C39" s="7">
@@ -3764,7 +4028,7 @@
       <c r="E39" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="6" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3772,7 +4036,7 @@
       <c r="A40" s="5">
         <v>46144</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="6" t="s">
         <v>66</v>
       </c>
       <c r="C40" s="7">
@@ -3784,7 +4048,127 @@
       <c r="E40" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F40" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="7">
+        <v>200000</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="7">
+        <v>60000</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="5">
+        <v>46145</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="7">
+        <v>306000</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="5">
+        <v>46172</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="7">
+        <v>16250</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="5">
+        <v>46146</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46950</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="3">
+        <v>46179</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="4">
+        <v>39000</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" s="25" t="s">
         <v>43</v>
       </c>
     </row>
